--- a/template_E.xlsx
+++ b/template_E.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/GitHub/GvsP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297D1B7A-3B15-6A45-9D19-584172A638E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BE6319-14E1-B041-90A5-5C44317FB7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17480" xr2:uid="{664D0AB6-784C-1D41-9706-1EA9FD4AD4C9}"/>
   </bookViews>
@@ -38,16 +38,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
-    <t>Low Multicollinearity</t>
-  </si>
-  <si>
-    <t>High Multicollinearity</t>
-  </si>
-  <si>
     <t xml:space="preserve"> f</t>
-  </si>
-  <si>
-    <t>Medium Multicollinearity</t>
   </si>
   <si>
     <t>E</t>
@@ -60,6 +51,15 @@
   </si>
   <si>
     <t>Opposite</t>
+  </si>
+  <si>
+    <t>Low Pleiotropy</t>
+  </si>
+  <si>
+    <t>Medium Pleiotropy</t>
+  </si>
+  <si>
+    <t>High Pleiotropy</t>
   </si>
 </sst>
 </file>
@@ -180,6 +180,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -188,9 +191,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -639,29 +639,29 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="D1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="10"/>
@@ -674,11 +674,11 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>0.1</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>5</v>
+      <c r="B3" s="14" t="s">
+        <v>2</v>
       </c>
       <c r="C3" s="3">
         <v>50</v>
@@ -694,8 +694,8 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="5">
         <v>150</v>
       </c>
@@ -710,8 +710,8 @@
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="7">
         <v>500</v>
       </c>
@@ -726,9 +726,9 @@
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="13" t="s">
-        <v>6</v>
+      <c r="A6" s="12"/>
+      <c r="B6" s="14" t="s">
+        <v>3</v>
       </c>
       <c r="C6" s="3">
         <v>50</v>
@@ -744,8 +744,8 @@
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
       <c r="C7" s="5">
         <v>150</v>
       </c>
@@ -760,8 +760,8 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="7">
         <v>500</v>
       </c>
@@ -776,9 +776,9 @@
       <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11" t="s">
-        <v>7</v>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="C9" s="5">
         <v>50</v>
@@ -794,8 +794,8 @@
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
       <c r="C10" s="5">
         <v>150</v>
       </c>
@@ -810,8 +810,8 @@
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="5">
         <v>500</v>
       </c>
@@ -826,11 +826,11 @@
       <c r="L11" s="8"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
+      <c r="A12" s="12">
         <v>0.5</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>5</v>
+      <c r="B12" s="14" t="s">
+        <v>2</v>
       </c>
       <c r="C12" s="3">
         <v>50</v>
@@ -846,8 +846,8 @@
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="5">
         <v>150</v>
       </c>
@@ -862,8 +862,8 @@
       <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="7">
         <v>500</v>
       </c>
@@ -878,9 +878,9 @@
       <c r="L14" s="8"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
-      <c r="B15" s="13" t="s">
-        <v>6</v>
+      <c r="A15" s="12"/>
+      <c r="B15" s="14" t="s">
+        <v>3</v>
       </c>
       <c r="C15" s="3">
         <v>50</v>
@@ -896,8 +896,8 @@
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
       <c r="C16" s="5">
         <v>150</v>
       </c>
@@ -912,8 +912,8 @@
       <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="7">
         <v>500</v>
       </c>
@@ -928,9 +928,9 @@
       <c r="L17" s="8"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11" t="s">
-        <v>7</v>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="C18" s="5">
         <v>50</v>
@@ -946,8 +946,8 @@
       <c r="L18" s="6"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
       <c r="C19" s="5">
         <v>150</v>
       </c>
@@ -962,8 +962,8 @@
       <c r="L19" s="6"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
       <c r="C20" s="7">
         <v>500</v>
       </c>
